--- a/胎壓檢測器資料庫_V10/MERCEDES-BENZ_Data.xlsx
+++ b/胎壓檢測器資料庫_V10/MERCEDES-BENZ_Data.xlsx
@@ -44229,7 +44229,7 @@
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>04/2007 -, 03/2014 - 05/2018, 06/2018 - 06/2023, 08/2024 -</t>
+          <t>04/2007 -, 03/2014 - 05/2018, 06/2018 - 06/2023, 08/2024 -, 08/2024 - 12/2026</t>
         </is>
       </c>
       <c r="H919" t="inlineStr">
@@ -45377,7 +45377,7 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>07/2024 -</t>
+          <t>07/2024 -, 08/2024 - 12/2026</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
@@ -45429,7 +45429,7 @@
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>04/2007 - 02/2014, 04/2007 -, 03/2014 - 05/2018, 06/2018 - 06/2023, 07/2024 -</t>
+          <t>04/2007 - 02/2014, 04/2007 -, 03/2014 - 05/2018, 06/2018 - 06/2023, 07/2024 -, 08/2024 - 12/2026</t>
         </is>
       </c>
       <c r="H947" t="inlineStr">
@@ -45481,7 +45481,7 @@
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>07/2024 -</t>
+          <t>07/2024 -, 08/2024 - 12/2026</t>
         </is>
       </c>
       <c r="H948" t="inlineStr">
